--- a/DB.xlsx
+++ b/DB.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B41"/>
+  <dimension ref="B2:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -553,105 +553,155 @@
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>이 아카이브의 174편은 아래 83개 핵심키워드로 다중 태깅되어 있습니다 (논문당 3~8개). 키워드로 논문을 찾으려면 [전체리스트] 시트의 핵심키워드 열 필터에서 '텍스트 포함' 조건으로 검색하세요.</t>
+          <t>이 아카이브의 174편은 아래 116개 핵심키워드로 다중 태깅되어 있으며, 5개 축(이론·개념 / 경험 설계 / 매체 &amp; 시스템 / 산업·응용 / 사례·IP)·하위그룹 체계로 분류했습니다. 키워드로 논문을 찾으려면 [전체리스트] 시트의 핵심키워드 열 필터에서 텍스트 포함 조건으로 검색하세요.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>■ 이론·개념</t>
+          <t>■ 이론·개념 (Theoretical Lenses)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>프레즌스(Presence) (15) · 플로우(Flow) (12) · 그룹플로우(Group Flow) (2) · 몰입이론(Immersion Theory) (25) · 매직서클(Magic Circle) (4) · 리미널리티(Liminality) (45) · 커뮤니타스(Communitas) (10) · 통과의례(Rite of Passage) (19) · 체현(Embodiment) (16) · 블리드(Bleed) (2) · 내러티브몰입(Narrative Absorption) (7) · 언캐니(Uncanny) (4) · 인지적소격(Cognitive Estrangement) (3) · 헤테로토피아(Heterotopia) (1) · 환상성(The Fantastic) (4) · 어포던스(Affordance) (2) · 파라소셜관계(Parasocial Relationship) (2) · 포스트휴먼(Posthuman) (2)</t>
+          <t>심리적 몰입 및 상태 : 현존감(Presence) (15) · 플로우(Flow) (13) · 그룹플로우(Group Flow) (2) · 몰입이론(Immersion Theory) (25) · 내러티브몰입(Narrative Absorption) (7) · 체현(Embodiment) (17) · 어포던스(Affordance) (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>인지적 낯설음 및 환상성 : 언캐니(Uncanny) (4) · 인지적소격(Cognitive Estrangement) (3) · 환상성(The Fantastic) (4) · 파라소셜관계(Parasocial Relationship) (2) · 포스트휴먼(Posthuman) (2)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>■ 경계·전이</t>
+          <t>전이성 및 사회적 의례 : 리미널리티(Liminality) (46) · 커뮤니타스(Communitas) (12) · 통과의례(Rite of Passage) (21) · 매직서클(Magic Circle) (4) · 블리드(Bleed) (2) · 리추얼(Ritual) (3)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>래빗홀(Rabbit Hole) (3) · 포탈(Portal) (6) · 문턱공간(Threshold Space) (18) · 일상(Everyday Life) (12) · 허구(Fiction) (10) · 백룸(Backrooms) (4) · 비장소(Non-place) (2)</t>
-        </is>
-      </c>
-    </row>
+          <t>경계 및 특수 공간 : 문턱공간(Threshold Space) (19) · 래빗홀(Rabbit Hole) (3) · 포탈(Portal) (6) · 백룸(Backrooms) (4) · 헤테로토피아(Heterotopia) (1) · 비장소(Non-place) (2) · 일상(Everyday Life) (12) · 허구(Fiction) (10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>■ 장르·형식</t>
+          <t>■ 경험 설계 (Experience Design)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>ARG (10) · LARP (5) · 퍼베이시브게임(Pervasive Game) (1) · 이머시브시어터(Immersive Theatre) (15) · 몰입형전시(Immersive Exhibition) (6) · 뮤지엄(Museum) (3) · VR (27) · AR (10) · 메타버스(Metaverse) (7) · 게임(Game) (29) · 웹소설(Web Novel) (4) · 이세계물(Isekai) (2) · 사변소설(Speculative Fiction) (8) · SF(Science Fiction) (8) · 판타지(Fantasy) (4) · 포탈판타지(Portal Fantasy) (5) · 미디어아트(Media Art) (7) · 다큐멘터리(Documentary) (3) · 애니메이션(Animation) (3)</t>
+          <t>세계관 &amp; 트랜스미디어 : 스토리텔링(Storytelling) (39) · 트랜스미디어(Transmedia) (19) · 세계관(Storyworld) (16) · 인터랙티브내러티브(Interactive Narrative) (15) · 월드빌딩(Worldbuilding) (11) · 캐논(Canon) (2) · 퀘스트디자인(Quest Design) (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>이야기 장르 : 사변소설(Speculative Fiction) (8) · SF(Science Fiction) (8) · 포탈판타지(Portal Fantasy) (5) · 판타지(Fantasy) (4) · 웹소설(Web Novel) (4) · 애니메이션(Animation) (3) · 다큐멘터리(Documentary) (3) · 이세계물(Isekai) (2)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>■ 디자인·방법</t>
+          <t>디자인 : 경험설계(Experience Design) (42) · 공간디자인(Spatial Design) (21) · UX디자인(UX Design) (12) · 건축(Architecture) (6) · 게이미피케이션(Gamification) (3)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>트랜스미디어(Transmedia) (19) · 인터랙티브내러티브(Interactive Narrative) (15) · 스토리텔링(Storytelling) (39) · 세계관(Storyworld) (16) · 월드빌딩(Worldbuilding) (11) · 캐논(Canon) (2) · 퀘스트디자인(Quest Design) (2) · UX디자인(UX Design) (12) · 게이미피케이션(Gamification) (3) · 공간디자인(Spatial Design) (21) · 건축(Architecture) (6) · 경험설계(Experience Design) (42) · 프로시저럴생성(Procedural Generation) (2) · 실시간렌더링(Real-time Rendering) (3) · 모션캡처(Motion Capture) (2) · 집단지성(Collective Intelligence) (1) · 디지털트윈(Digital Twin) (1)</t>
+      <c r="B32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>■ 매체 &amp; 시스템 (Media &amp; Systems)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>■ 산업·응용</t>
+          <t>경험 형식 : 게임(Game) (29) · 이머시브시어터(Immersive Theatre) (15) · ARG (10) · 몰입형전시(Immersive Exhibition) (6) · LARP (5) · 뮤지엄(Museum) (3) · 퍼베이시브게임(Pervasive Game) (1)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>K-pop (16) · 팬덤(Fandom) (21) · 팬노동(Fan Labor) (2) · 팬픽션(Fanfiction) (1) · 브랜드경험(Brand Experience) (10) · 팝업스토어(Pop-up Store) (1) · IP (9) · 프랜차이즈(Franchise) (5) · 버추얼아이돌(Virtual Idol) (4) · 버추얼프로덕션(Virtual Production) (4) · 생성형AI(Generative AI) (6) · LLM (1) · 교육(Education) (14) · 학습(Learning) (13) · 관광(Tourism) (4) · 페스티벌(Festival) (1) · 소비자행동(Consumer Behavior) (16) · 피지털(Phygital) (1)</t>
-        </is>
-      </c>
-    </row>
+          <t>기술·플랫폼 : VR (27) · AR (10) · 메타버스(Metaverse) (7) · 미디어아트(Media Art) (7) · 생성형AI(Generative AI) (6) · 버추얼프로덕션(Virtual Production) (4) · 실시간렌더링(Real-time Rendering) (3) · 프로시저럴생성(Procedural Generation) (2) · 모션캡처(Motion Capture) (2) · 언리얼엔진(Unreal Engine) (2) · 디지털트윈(Digital Twin) (1) · LLM (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>■ 관점</t>
+          <t>■ 산업·응용 (Industry &amp; Application)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>관객성(Spectatorship) (16) · 참여(Participation) (30) · 상호작용(Interaction) (12) · 아바타(Avatar) (7)</t>
+          <t>수용자 참여·행동 : 참여(Participation) (30) · 팬덤(Fandom) (21) · 관객성(Spectatorship) (16) · 소비자행동(Consumer Behavior) (16) · 상호작용(Interaction) (12) · 아바타(Avatar) (7) · 팬노동(Fan Labor) (2) · 팬픽션(Fanfiction) (1) · 집단지성(Collective Intelligence) (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>적용 산업·분야 : K-pop (16) · 교육(Education) (14) · 학습(Learning) (13) · 브랜드경험(Brand Experience) (10) · IP (9) · 프랜차이즈(Franchise) (5) · 버추얼아이돌(Virtual Idol) (4) · 관광(Tourism) (4) · 팝업스토어(Pop-up Store) (1) · 페스티벌(Festival) (2) · 피지털(Phygital) (1)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>■ 사례·IP</t>
-        </is>
-      </c>
+      <c r="B40" s="6" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>방탄소년단(BTS) (1) · SMCU (1) · NEO PARASPECTRUM (1) · 엔하이픈(ENHYPEN) (1) · 앤팀(&amp;TEAM) (1) · 다크문(Dark Moon) (1) · 위버스(Weverse) (1) · 팝마트(POP MART) (1) · 플레이브(PLAVE) (2) · K/DA (1) · GOT7 (1) · 팀랩(teamLab) (1) · 슬립노모어(Sleep No More) (1) · 버닝필드(Burning Field) (1) · 댄쉬펠(Dan Shpiel) (1) · 비욘더로드(Beyond the Road) (1) · 메모리얼조용한식탁(Memorial: The Quiet Table) (1) · 디트로이트비컴휴먼(Detroit: Become Human) (1) · 월드오브워크래프트(World of Warcraft) (1) · MCU (1) · 마블(Marvel) (1) · DC (1) · 스타워즈(Star Wars) (1) · 나니아(Narnia) (1) · 조커(Joker) (1) · 토지(Toji) (1) · 소환희(Sohwanhui) (1) · 한강(Han Kang) (1) · 제로데이즈(Zero Days) (1) · Wishbowl (1) · ARGOSI (1) · 언리얼엔진(Unreal Engine) (2)</t>
+          <t>■ 사례·IP (Case Corpus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>K-pop &amp; 팬덤 : 방탄소년단(BTS) (1) · SMCU (1) · NEO PARASPECTRUM (1) · 엔하이픈(ENHYPEN) (1) · 앤팀(&amp;TEAM) (1) · 다크문(Dark Moon) (1) · 위버스(Weverse) (1) · 플레이브(PLAVE) (2) · K/DA (1) · GOT7 (1) · 팝마트(POP MART) (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>이머시브 공연·전시 : 슬립노모어(Sleep No More) (1) · 버닝필드(Burning Field) (1) · 댄쉬펠(Dan Shpiel) (1) · 비욘더로드(Beyond the Road) (1) · 메모리얼조용한식탁(Memorial: The Quiet Table) (1) · 팀랩(teamLab) (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>게임·엔터·IP 사례 : 디트로이트비컴휴먼(Detroit: Become Human) (1) · 월드오브워크래프트(World of Warcraft) (1) · 제로데이즈(Zero Days) (1) · Wishbowl (1) · ARGOSI (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>문학·기타 콘텐츠 : MCU (1) · 마블(Marvel) (1) · DC (1) · 스타워즈(Star Wars) (1) · 나니아(Narnia) (1) · 조커(Joker) (1) · 토지(Toji) (1) · 소환희(Sohwanhui) (1) · 한강(Han Kang) (1)</t>
         </is>
       </c>
     </row>
@@ -788,7 +838,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -832,7 +881,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -924,7 +972,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1056,7 +1103,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -1064,7 +1111,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1100,7 +1146,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), 플로우(Flow)</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -1108,7 +1154,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1192,7 +1237,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 게임(Game), 플로우(Flow)</t>
+          <t>현존감(Presence), VR, 게임(Game), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -1200,7 +1245,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -1248,7 +1292,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1292,7 +1335,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1328,7 +1370,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>VR, 프레즌스(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
+          <t>VR, 현존감(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -1336,7 +1378,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1372,7 +1413,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), VR, 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -1420,7 +1461,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -1428,7 +1469,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1472,7 +1512,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1516,7 +1555,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1560,7 +1598,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1604,7 +1641,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1696,7 +1732,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1792,7 +1827,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -1892,7 +1926,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -1992,7 +2025,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2088,7 +2120,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -2136,7 +2167,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -2184,7 +2214,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2228,7 +2257,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -2276,7 +2304,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -2376,7 +2403,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2472,7 +2498,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -2520,7 +2545,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2564,7 +2588,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -2612,7 +2635,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -2712,7 +2734,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2756,7 +2777,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2800,7 +2820,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2892,7 +2911,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2936,7 +2954,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2980,7 +2997,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3024,7 +3040,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3068,7 +3083,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3104,7 +3118,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), VR, 프레즌스(Presence)</t>
+          <t>체현(Embodiment), 아바타(Avatar), VR, 현존감(Presence)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -3112,7 +3126,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3204,7 +3217,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
@@ -3300,7 +3312,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너</t>
@@ -3348,7 +3359,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
@@ -3392,7 +3402,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3436,7 +3445,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3480,7 +3488,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
@@ -3524,7 +3531,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3568,7 +3574,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3604,7 +3609,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 프레즌스(Presence), 체현(Embodiment)</t>
+          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 현존감(Presence), 체현(Embodiment)</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -3612,7 +3617,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러, VR 콘텐츠 디자이너</t>
@@ -3660,7 +3664,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -3708,7 +3711,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
@@ -3852,7 +3854,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
@@ -3896,7 +3897,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3940,7 +3940,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3984,7 +3983,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
@@ -4028,7 +4026,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
@@ -4112,7 +4109,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>AR, 프레즌스(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
+          <t>AR, 현존감(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
@@ -4120,7 +4117,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
@@ -4164,7 +4160,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
@@ -4208,7 +4203,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4300,7 +4294,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
@@ -4344,7 +4337,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
@@ -4380,7 +4372,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
+          <t>현존감(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -4440,7 +4432,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너, 실시간 애니메이터</t>
@@ -4488,7 +4479,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
@@ -4532,7 +4522,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -4572,7 +4561,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), VR, AR</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), VR, AR</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -4580,7 +4569,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -4620,7 +4608,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), 프레즌스(Presence), VR, 메타버스(Metaverse)</t>
+          <t>체현(Embodiment), 아바타(Avatar), 현존감(Presence), VR, 메타버스(Metaverse)</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -4628,7 +4616,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -4676,7 +4663,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -4724,7 +4710,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -4764,7 +4749,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4772,7 +4757,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4816,7 +4800,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -4856,7 +4839,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -4864,7 +4847,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -4960,7 +4942,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -5008,7 +4989,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -5056,7 +5036,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
@@ -5152,7 +5131,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
@@ -5196,7 +5174,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -5244,7 +5221,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -5344,7 +5320,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -5440,7 +5415,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
@@ -5476,7 +5450,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>VR, 학습(Learning), 프레즌스(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
+          <t>VR, 학습(Learning), 현존감(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -5484,7 +5458,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
@@ -5528,7 +5501,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
@@ -5572,7 +5544,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
@@ -5616,7 +5587,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
@@ -5712,7 +5682,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -5760,7 +5729,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, IP 개발 기획자</t>
@@ -5860,7 +5828,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, IP 개발 기획자</t>
@@ -5908,7 +5875,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자, IP 개발 기획자</t>
@@ -6008,7 +5974,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너, 실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -6056,7 +6021,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" s="5" t="inlineStr">
         <is>
           <t>IP 개발 기획자, 실시간 애니메이터</t>
@@ -6104,7 +6068,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -6152,7 +6115,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -6252,7 +6214,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -6352,7 +6313,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트, 게임 스토리 작가</t>
@@ -6452,7 +6412,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -6500,7 +6459,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
@@ -6544,7 +6502,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -6592,7 +6549,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
@@ -6636,7 +6592,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
@@ -6732,7 +6687,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -6780,7 +6734,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
@@ -6824,7 +6777,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
@@ -6868,7 +6820,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -6916,7 +6867,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자</t>
@@ -6964,7 +6914,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -7012,7 +6961,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
@@ -7056,7 +7004,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
@@ -7100,7 +7047,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -7148,7 +7094,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -7196,7 +7141,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -7244,7 +7188,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
@@ -7288,7 +7231,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
@@ -7380,7 +7322,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
@@ -7424,7 +7365,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -7472,7 +7412,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -7520,7 +7459,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -7568,7 +7506,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -7616,7 +7553,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -7664,7 +7600,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -7712,7 +7647,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" s="5" t="inlineStr"/>
     </row>
     <row r="153">
@@ -7756,7 +7690,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -7804,7 +7737,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
@@ -7848,7 +7780,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -7896,7 +7827,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -7944,7 +7874,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
@@ -7988,7 +7917,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, XR 경험 디자이너</t>
@@ -8036,7 +7964,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
@@ -8080,7 +8007,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" s="5" t="inlineStr"/>
     </row>
     <row r="161">
@@ -8124,7 +8050,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
@@ -8168,7 +8093,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -8216,7 +8140,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -8264,7 +8187,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -8312,7 +8234,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
@@ -8356,7 +8277,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -8404,7 +8324,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
@@ -8448,7 +8367,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -8496,7 +8414,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" s="5" t="inlineStr"/>
     </row>
     <row r="170">
@@ -8540,7 +8457,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -8588,7 +8504,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -8636,7 +8551,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -8836,7 +8750,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" s="5" t="inlineStr"/>
     </row>
     <row r="177">
@@ -9241,7 +9154,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -9285,7 +9197,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -9377,7 +9288,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -9509,7 +9419,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -9517,7 +9427,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
@@ -9553,7 +9462,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), 플로우(Flow)</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -9561,7 +9470,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
@@ -9645,7 +9553,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 게임(Game), 플로우(Flow)</t>
+          <t>현존감(Presence), VR, 게임(Game), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -9653,7 +9561,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -9701,7 +9608,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
@@ -9745,7 +9651,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
@@ -9781,7 +9686,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>VR, 프레즌스(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
+          <t>VR, 현존감(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -9789,7 +9694,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
@@ -9825,7 +9729,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), VR, 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -9873,7 +9777,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -9881,7 +9785,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
@@ -9925,7 +9828,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -9969,7 +9871,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
@@ -10013,7 +9914,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -10057,7 +9957,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -10149,7 +10048,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
@@ -10245,7 +10143,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -10345,7 +10242,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -10445,7 +10341,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -10541,7 +10436,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -10589,7 +10483,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -10637,7 +10530,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
@@ -10681,7 +10573,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -10729,7 +10620,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -10829,7 +10719,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
@@ -10925,7 +10814,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -10973,7 +10861,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
@@ -11017,7 +10904,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -11065,7 +10951,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -11165,7 +11050,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
@@ -11209,7 +11093,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
@@ -11253,7 +11136,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
@@ -11345,7 +11227,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
@@ -11389,7 +11270,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
@@ -11433,7 +11313,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
@@ -11477,7 +11356,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
@@ -11521,7 +11399,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
@@ -11557,7 +11434,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), VR, 프레즌스(Presence)</t>
+          <t>체현(Embodiment), 아바타(Avatar), VR, 현존감(Presence)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -11565,7 +11442,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
@@ -11657,7 +11533,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
@@ -11753,7 +11628,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너</t>
@@ -11801,7 +11675,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
@@ -11845,7 +11718,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
@@ -11889,7 +11761,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
@@ -11933,7 +11804,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
@@ -11977,7 +11847,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
@@ -12021,7 +11890,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
@@ -12057,7 +11925,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 프레즌스(Presence), 체현(Embodiment)</t>
+          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 현존감(Presence), 체현(Embodiment)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -12065,7 +11933,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러, VR 콘텐츠 디자이너</t>
@@ -12113,7 +11980,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -12161,7 +12027,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
@@ -12305,7 +12170,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
@@ -12349,7 +12213,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
@@ -12393,7 +12256,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
@@ -12437,7 +12299,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
@@ -12481,7 +12342,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
@@ -12565,7 +12425,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>AR, 프레즌스(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
+          <t>AR, 현존감(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
@@ -12573,7 +12433,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
@@ -12617,7 +12476,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
@@ -12661,7 +12519,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
@@ -12753,7 +12610,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
@@ -12797,7 +12653,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
@@ -12833,7 +12688,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
+          <t>현존감(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -12893,7 +12748,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너, 실시간 애니메이터</t>
@@ -12941,7 +12795,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
@@ -12985,7 +12838,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -13025,7 +12877,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), VR, AR</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), VR, AR</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -13033,7 +12885,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -13073,7 +12924,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), 프레즌스(Presence), VR, 메타버스(Metaverse)</t>
+          <t>체현(Embodiment), 아바타(Avatar), 현존감(Presence), VR, 메타버스(Metaverse)</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -13081,7 +12932,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -13129,7 +12979,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -13177,7 +13026,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -13217,7 +13065,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -13225,7 +13073,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
@@ -13269,7 +13116,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -13309,7 +13155,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -13317,7 +13163,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -13413,7 +13258,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -13461,7 +13305,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -13509,7 +13352,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
@@ -13605,7 +13447,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
@@ -13649,7 +13490,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -13697,7 +13537,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -13797,7 +13636,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -13893,7 +13731,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
@@ -13929,7 +13766,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>VR, 학습(Learning), 프레즌스(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
+          <t>VR, 학습(Learning), 현존감(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -13937,7 +13774,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
@@ -13981,7 +13817,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
@@ -14025,7 +13860,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
@@ -14069,7 +13903,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
@@ -14165,7 +13998,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -14213,7 +14045,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, IP 개발 기획자</t>
@@ -14313,7 +14144,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, IP 개발 기획자</t>
@@ -14361,7 +14191,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자, IP 개발 기획자</t>
@@ -14461,7 +14290,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너, 실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -14509,7 +14337,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" s="5" t="inlineStr">
         <is>
           <t>IP 개발 기획자, 실시간 애니메이터</t>
@@ -14557,7 +14384,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -14605,7 +14431,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -14705,7 +14530,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -14805,7 +14629,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트, 게임 스토리 작가</t>
@@ -14905,7 +14728,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -14953,7 +14775,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
@@ -14997,7 +14818,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -15045,7 +14865,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
@@ -15089,7 +14908,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
@@ -15185,7 +15003,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -15233,7 +15050,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
@@ -15277,7 +15093,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
@@ -15321,7 +15136,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -15369,7 +15183,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자</t>
@@ -15417,7 +15230,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -15465,7 +15277,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
@@ -15509,7 +15320,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
@@ -15553,7 +15363,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -15601,7 +15410,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -15649,7 +15457,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -15697,7 +15504,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
@@ -15741,7 +15547,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
@@ -15833,7 +15638,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
@@ -15877,7 +15681,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -15925,7 +15728,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -15973,7 +15775,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -16021,7 +15822,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -16069,7 +15869,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -16117,7 +15916,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -16165,7 +15963,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
@@ -16209,7 +16006,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -16257,7 +16053,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
@@ -16301,7 +16096,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -16349,7 +16143,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -16397,7 +16190,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
@@ -16441,7 +16233,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, XR 경험 디자이너</t>
@@ -16489,7 +16280,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
@@ -16533,7 +16323,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
@@ -16577,7 +16366,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" s="5" t="inlineStr"/>
     </row>
     <row r="161">
@@ -16621,7 +16409,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -16669,7 +16456,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -16717,7 +16503,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -16765,7 +16550,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
@@ -16809,7 +16593,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -16857,7 +16640,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
@@ -16901,7 +16683,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -16949,7 +16730,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
@@ -16993,7 +16773,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -17041,7 +16820,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -17089,7 +16867,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -17289,7 +17066,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" s="5" t="inlineStr"/>
     </row>
     <row r="176">
@@ -17680,7 +17456,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -17724,7 +17499,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -17768,7 +17542,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -17812,7 +17585,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -17856,7 +17628,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -17948,7 +17719,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
@@ -18044,7 +17814,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너</t>
@@ -18192,7 +17961,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
@@ -18228,7 +17996,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
+          <t>현존감(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -18288,7 +18056,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너, 실시간 애니메이터</t>
@@ -18336,7 +18103,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
@@ -18380,7 +18146,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -18420,7 +18185,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), VR, AR</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), VR, AR</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -18428,7 +18193,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -18468,7 +18232,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), 프레즌스(Presence), VR, 메타버스(Metaverse)</t>
+          <t>체현(Embodiment), 아바타(Avatar), 현존감(Presence), VR, 메타버스(Metaverse)</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -18476,7 +18240,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -18524,7 +18287,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -18572,7 +18334,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -18620,7 +18381,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -18720,7 +18480,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -18820,7 +18579,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -18868,7 +18626,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
@@ -18912,7 +18669,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -19008,7 +18764,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -19056,7 +18811,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
@@ -19100,7 +18854,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
@@ -19144,7 +18897,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
@@ -19236,7 +18988,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
@@ -19332,7 +19083,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -19428,7 +19178,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
@@ -19472,7 +19221,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
@@ -19516,7 +19264,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
@@ -19560,7 +19307,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
@@ -19604,7 +19350,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
@@ -19640,7 +19385,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -19648,7 +19393,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
@@ -19692,7 +19436,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -19844,7 +19587,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -19892,7 +19634,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너, 실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -19940,7 +19681,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr">
         <is>
           <t>IP 개발 기획자, 실시간 애니메이터</t>
@@ -19988,7 +19728,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -20036,7 +19775,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -20136,7 +19874,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
@@ -20180,7 +19917,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -20376,7 +20112,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
@@ -20420,7 +20155,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
@@ -20464,7 +20198,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
@@ -20508,7 +20241,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
@@ -20544,7 +20276,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -20552,7 +20284,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -20648,7 +20379,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -20696,7 +20426,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -20744,7 +20473,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
@@ -20788,7 +20516,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -20836,7 +20563,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자</t>
@@ -20884,7 +20610,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -20932,7 +20657,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -21032,7 +20756,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
@@ -21076,7 +20799,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
@@ -21120,7 +20842,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
@@ -21164,7 +20885,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
@@ -21208,7 +20928,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
@@ -21304,7 +21023,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
@@ -21396,7 +21114,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
@@ -21440,7 +21157,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
@@ -21484,7 +21200,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -21532,7 +21247,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -21580,7 +21294,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
@@ -21676,7 +21389,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -21724,7 +21436,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -21772,7 +21483,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
@@ -21808,7 +21518,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), VR, 프레즌스(Presence)</t>
+          <t>체현(Embodiment), 아바타(Avatar), VR, 현존감(Presence)</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -21816,7 +21526,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
@@ -21860,7 +21569,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -21908,7 +21616,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
@@ -21952,7 +21659,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
@@ -21988,7 +21694,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -21996,7 +21702,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
@@ -22040,7 +21745,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
@@ -22124,7 +21828,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>AR, 프레즌스(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
+          <t>AR, 현존감(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -22132,7 +21836,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
@@ -22176,7 +21879,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, IP 개발 기획자</t>
@@ -22324,7 +22026,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
@@ -22368,7 +22069,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -22464,7 +22164,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
@@ -22500,7 +22199,7 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 프레즌스(Presence), 체현(Embodiment)</t>
+          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 현존감(Presence), 체현(Embodiment)</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -22508,7 +22207,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러, VR 콘텐츠 디자이너</t>
@@ -22556,7 +22254,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, IP 개발 기획자</t>
@@ -22604,7 +22301,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -22652,7 +22348,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -22700,7 +22395,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -22740,7 +22434,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), 플로우(Flow)</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -22748,7 +22442,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
@@ -22840,7 +22533,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -22888,7 +22580,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -22936,7 +22627,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -22984,7 +22674,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
@@ -23020,7 +22709,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>VR, 학습(Learning), 프레즌스(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
+          <t>VR, 학습(Learning), 현존감(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
@@ -23028,7 +22717,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
@@ -23072,7 +22760,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -23120,7 +22807,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -23160,7 +22846,7 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 게임(Game), 플로우(Flow)</t>
+          <t>현존감(Presence), VR, 게임(Game), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
@@ -23168,7 +22854,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -23216,7 +22901,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
@@ -23260,7 +22944,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
@@ -23304,7 +22987,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
@@ -23348,7 +23030,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
@@ -23392,7 +23073,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
@@ -23436,7 +23116,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -23484,7 +23163,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -23532,7 +23210,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
@@ -23576,7 +23253,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
@@ -23672,7 +23348,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
@@ -23716,7 +23391,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
@@ -23760,7 +23434,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
@@ -23804,7 +23477,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트, 게임 스토리 작가</t>
@@ -23852,7 +23524,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -23952,7 +23623,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -24000,7 +23670,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자, IP 개발 기획자</t>
@@ -24048,7 +23717,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -24096,7 +23764,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
@@ -24140,7 +23807,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
@@ -24184,7 +23850,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, XR 경험 디자이너</t>
@@ -24232,7 +23897,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
@@ -24276,7 +23940,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
@@ -24320,7 +23983,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
@@ -24364,7 +24026,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" s="5" t="inlineStr"/>
     </row>
     <row r="147">
@@ -24400,7 +24061,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>VR, 프레즌스(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
+          <t>VR, 현존감(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
@@ -24408,7 +24069,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" s="5" t="inlineStr"/>
     </row>
     <row r="148">
@@ -24452,7 +24112,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -24500,7 +24159,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -24700,7 +24358,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -24748,7 +24405,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -24796,7 +24452,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -24844,7 +24499,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -24892,7 +24546,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
@@ -24936,7 +24589,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
@@ -24980,7 +24632,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
@@ -25024,7 +24675,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -25072,7 +24722,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
@@ -25116,7 +24765,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -25156,7 +24804,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), VR, 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
@@ -25204,7 +24852,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H164" s="10" t="inlineStr">
@@ -25212,7 +24860,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
@@ -25256,7 +24903,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
@@ -25300,7 +24946,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -25348,7 +24993,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -25396,7 +25040,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -25548,7 +25191,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" s="5" t="inlineStr"/>
     </row>
     <row r="172">
@@ -25592,7 +25234,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" s="5" t="inlineStr"/>
     </row>
     <row r="173">
@@ -25636,7 +25277,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" s="5" t="inlineStr"/>
     </row>
     <row r="174">
@@ -25728,7 +25368,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" s="5" t="inlineStr"/>
     </row>
     <row r="176">
@@ -26319,7 +25958,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -26367,7 +26005,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -26451,7 +26088,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -26459,7 +26096,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
@@ -26495,7 +26131,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -26503,7 +26139,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -26551,7 +26186,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -26599,7 +26233,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너, 실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -26695,7 +26328,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
@@ -26839,7 +26471,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -26931,7 +26562,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -26975,7 +26605,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -27071,7 +26700,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
@@ -27163,7 +26791,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
@@ -27207,7 +26834,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
@@ -27251,7 +26877,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
@@ -27295,7 +26920,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
@@ -27339,7 +26963,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -27383,7 +27006,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자</t>
@@ -27423,7 +27045,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
+          <t>현존감(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -27483,7 +27105,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -27531,7 +27152,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
@@ -27575,7 +27195,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
@@ -27667,7 +27286,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
@@ -27711,7 +27329,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
@@ -27855,7 +27472,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
@@ -27899,7 +27515,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -27947,7 +27562,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -28047,7 +27661,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, IP 개발 기획자</t>
@@ -28095,7 +27708,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -28191,7 +27803,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -28239,7 +27850,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -28287,7 +27897,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
@@ -28331,7 +27940,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
@@ -28375,7 +27983,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
@@ -28471,7 +28078,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -28511,7 +28117,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -28519,7 +28125,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
@@ -28563,7 +28168,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
@@ -28655,7 +28259,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
@@ -28747,7 +28350,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
@@ -28843,7 +28445,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, IP 개발 기획자</t>
@@ -28891,7 +28492,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -28939,7 +28539,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -28987,7 +28586,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
@@ -29031,7 +28629,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
@@ -29127,7 +28724,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
@@ -29171,7 +28767,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
@@ -29215,7 +28810,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
@@ -29259,7 +28853,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자, IP 개발 기획자</t>
@@ -29307,7 +28900,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
@@ -29351,7 +28943,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -29399,7 +28990,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -29447,7 +29037,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
@@ -29491,7 +29080,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, XR 경험 디자이너</t>
@@ -29539,7 +29127,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -29587,7 +29174,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -29627,7 +29213,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>VR, 프레즌스(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
+          <t>VR, 현존감(Presence), 내러티브몰입(Narrative Absorption), 다큐멘터리(Documentary), 스토리텔링(Storytelling)</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -29635,7 +29221,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
@@ -29671,7 +29256,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), VR, 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -29727,7 +29312,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
@@ -29771,7 +29355,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -29819,7 +29402,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -29867,7 +29449,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -29915,7 +29496,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -29963,7 +29543,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
@@ -30055,7 +29634,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
@@ -30099,7 +29677,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
@@ -30143,7 +29720,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -30191,7 +29767,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
@@ -30287,7 +29862,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -30335,7 +29909,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -30383,7 +29956,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
@@ -30475,7 +30047,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -30523,7 +30094,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -30623,7 +30193,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
@@ -30667,7 +30236,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
@@ -30711,7 +30279,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
@@ -30755,7 +30322,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -30795,7 +30361,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), 플로우(Flow)</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -30803,7 +30369,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
@@ -30847,7 +30412,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -30895,7 +30459,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
@@ -30939,7 +30502,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -30987,7 +30549,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -31035,7 +30596,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
@@ -31079,7 +30639,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
@@ -31123,7 +30682,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너</t>
@@ -31171,7 +30729,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
@@ -31215,7 +30772,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -31263,7 +30819,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -31303,7 +30858,7 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>AR, 프레즌스(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
+          <t>AR, 현존감(Presence), 플로우(Flow), 소비자행동(Consumer Behavior), 브랜드경험(Brand Experience)</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -31311,7 +30866,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
@@ -31355,7 +30909,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너, 실시간 애니메이터</t>
@@ -31611,7 +31164,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
@@ -31655,7 +31207,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
@@ -31691,7 +31242,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>VR, 학습(Learning), 프레즌스(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
+          <t>VR, 학습(Learning), 현존감(Presence), 몰입이론(Immersion Theory), 교육(Education)</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
@@ -31699,7 +31250,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
@@ -31847,7 +31397,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
@@ -31891,7 +31440,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr">
         <is>
           <t>IP 개발 기획자, 실시간 애니메이터</t>
@@ -31939,7 +31487,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -31987,7 +31534,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
@@ -32023,7 +31569,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 프레즌스(Presence), 체현(Embodiment)</t>
+          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 현존감(Presence), 체현(Embodiment)</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
@@ -32031,7 +31577,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러, VR 콘텐츠 디자이너</t>
@@ -32079,7 +31624,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -32127,7 +31671,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
@@ -32171,7 +31714,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -32219,7 +31761,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
@@ -32263,7 +31804,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
@@ -32307,7 +31847,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -32355,7 +31894,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -32403,7 +31941,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
@@ -32447,7 +31984,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
@@ -32491,7 +32027,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -32539,7 +32074,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
@@ -32583,7 +32117,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
@@ -32619,7 +32152,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 게임(Game), 플로우(Flow)</t>
+          <t>현존감(Presence), VR, 게임(Game), 플로우(Flow)</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
@@ -32627,7 +32160,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -32675,7 +32207,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -32723,7 +32254,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
@@ -32767,7 +32297,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -32815,7 +32344,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -32863,7 +32391,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -32911,7 +32438,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -32959,7 +32485,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
@@ -32995,7 +32520,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), VR, AR</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), VR, AR</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
@@ -33003,7 +32528,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -33043,7 +32567,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), 프레즌스(Presence), VR, 메타버스(Metaverse)</t>
+          <t>체현(Embodiment), 아바타(Avatar), 현존감(Presence), VR, 메타버스(Metaverse)</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
@@ -33051,7 +32575,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -33099,7 +32622,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" s="5" t="inlineStr"/>
     </row>
     <row r="153">
@@ -33135,7 +32657,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
+          <t>현존감(Presence), 플로우(Flow), 내러티브몰입(Narrative Absorption), 몰입이론(Immersion Theory)</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
@@ -33143,7 +32665,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
@@ -33287,7 +32808,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트, 게임 스토리 작가</t>
@@ -33335,7 +32855,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
@@ -33379,7 +32898,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
@@ -33423,7 +32941,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -33471,7 +32988,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" s="5" t="inlineStr"/>
     </row>
     <row r="161">
@@ -33515,7 +33031,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -33563,7 +33078,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -33611,7 +33125,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" s="5" t="inlineStr"/>
     </row>
     <row r="164">
@@ -33655,7 +33168,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -33695,7 +33207,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), VR, 프레즌스(Presence)</t>
+          <t>체현(Embodiment), 아바타(Avatar), VR, 현존감(Presence)</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
@@ -33703,7 +33215,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
@@ -33747,7 +33258,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
@@ -33791,7 +33301,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
@@ -33835,7 +33344,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
@@ -33931,7 +33439,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" s="5" t="inlineStr"/>
     </row>
     <row r="171">
@@ -33975,7 +33482,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -34023,7 +33529,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -34071,7 +33576,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -34119,7 +33623,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" s="5" t="inlineStr"/>
     </row>
     <row r="175">
@@ -34215,7 +33718,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -34569,7 +34071,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -34679,7 +34180,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -34732,7 +34232,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -34899,7 +34398,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -34952,7 +34450,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -35062,7 +34559,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, IP 개발 기획자</t>
@@ -35115,7 +34611,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자, IP 개발 기획자</t>
@@ -35168,7 +34663,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -35221,7 +34715,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자</t>
@@ -35274,7 +34767,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -35327,7 +34819,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -35380,7 +34871,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서</t>
@@ -35547,7 +35037,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -35600,7 +35089,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -35653,7 +35141,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -35763,7 +35250,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -35873,7 +35359,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -35926,7 +35411,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -35979,7 +35463,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -36032,7 +35515,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너</t>
@@ -36085,7 +35567,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36138,7 +35619,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -36248,7 +35728,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36358,7 +35837,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, IP 개발 기획자</t>
@@ -36411,7 +35889,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자, IP 개발 기획자</t>
@@ -36464,7 +35941,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자</t>
@@ -36517,7 +35993,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36570,7 +36045,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36623,7 +36097,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36676,7 +36149,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36729,7 +36201,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36782,7 +36253,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, XR 경험 디자이너</t>
@@ -36835,7 +36305,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36888,7 +36357,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36941,7 +36409,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -36994,7 +36461,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자</t>
@@ -37153,7 +36619,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
+          <t>현존감(Presence), 체현(Embodiment), 아바타(Avatar), VR</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -37210,7 +36676,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>몰입이론(Immersion Theory), 프레즌스(Presence), VR, AR</t>
+          <t>몰입이론(Immersion Theory), 현존감(Presence), VR, AR</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -37218,7 +36684,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37263,7 +36728,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>체현(Embodiment), 아바타(Avatar), 프레즌스(Presence), VR, 메타버스(Metaverse)</t>
+          <t>체현(Embodiment), 아바타(Avatar), 현존감(Presence), VR, 메타버스(Metaverse)</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -37271,7 +36736,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37324,7 +36788,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37377,7 +36840,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -37422,7 +36884,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), 몰입이론(Immersion Theory), VR</t>
+          <t>현존감(Presence), 몰입이론(Immersion Theory), VR</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -37430,7 +36892,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37483,7 +36944,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -37593,7 +37053,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37703,7 +37162,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37756,7 +37214,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37809,7 +37266,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -37862,7 +37318,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, XR 경험 디자이너</t>
@@ -37915,7 +37370,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너</t>
@@ -38082,7 +37536,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -38135,7 +37588,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러</t>
@@ -38188,7 +37640,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -38233,7 +37684,7 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 프레즌스(Presence), 체현(Embodiment)</t>
+          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 현존감(Presence), 체현(Embodiment)</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -38241,7 +37692,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러, VR 콘텐츠 디자이너</t>
@@ -38294,7 +37744,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -38347,7 +37796,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -38400,7 +37848,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러</t>
@@ -38510,7 +37957,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -38620,7 +38066,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트</t>
@@ -38730,7 +38175,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트, 게임 스토리 작가</t>
@@ -38840,7 +38284,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 세계관 기획자, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -38950,7 +38393,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" s="5" t="inlineStr">
         <is>
           <t>생성형 미디어 아티스트, 게임 스토리 작가</t>
@@ -39060,7 +38502,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" s="5" t="inlineStr">
         <is>
           <t>내러티브 디자이너, 인터랙티브 스토리텔러, 게임 스토리 작가</t>
@@ -39170,7 +38611,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너</t>
@@ -39223,7 +38663,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -39276,7 +38715,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너, 실시간 애니메이터</t>
@@ -39329,7 +38767,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" s="5" t="inlineStr">
         <is>
           <t>XR 경험 디자이너, 메타버스 경험 디자이너</t>
@@ -39431,7 +38868,7 @@
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>프레즌스(Presence), VR, 게임(Game), 플로우(Flow)</t>
+          <t>현존감(Presence), VR, 게임(Game), 플로우(Flow)</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -39439,7 +38876,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -39492,7 +38928,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -39537,7 +38972,7 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 프레즌스(Presence), 체현(Embodiment)</t>
+          <t>UX디자인(UX Design), VR, 인터랙티브내러티브(Interactive Narrative), 현존감(Presence), 체현(Embodiment)</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -39545,7 +38980,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" s="5" t="inlineStr">
         <is>
           <t>인터랙티브 스토리텔러, VR 콘텐츠 디자이너</t>
@@ -39598,7 +39032,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -39651,7 +39084,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너</t>
@@ -39761,7 +39193,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너, 실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -39814,7 +39245,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -39867,7 +39297,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -39920,7 +39349,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -39973,7 +39401,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서</t>
@@ -40083,7 +39510,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너, 실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -40136,7 +39562,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -40303,7 +39728,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, IP 개발 기획자</t>
@@ -40413,7 +39837,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" s="5" t="inlineStr">
         <is>
           <t>세계관 기획자, IP 개발 기획자</t>
@@ -40466,7 +39889,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" s="5" t="inlineStr">
         <is>
           <t>트랜스미디어 프로듀서, 세계관 기획자, IP 개발 기획자</t>
@@ -40519,7 +39941,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" s="5" t="inlineStr">
         <is>
           <t>IP 개발 기획자, 실시간 애니메이터</t>
@@ -40629,7 +40050,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" s="5" t="inlineStr">
         <is>
           <t>메타버스 경험 디자이너, 실시간 애니메이터</t>
@@ -40739,7 +40159,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" s="5" t="inlineStr">
         <is>
           <t>VR 콘텐츠 디자이너, 실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
@@ -40792,7 +40211,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" s="5" t="inlineStr">
         <is>
           <t>IP 개발 기획자, 실시간 애니메이터</t>
@@ -40845,7 +40263,6 @@
           <t>열기</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" s="5" t="inlineStr">
         <is>
           <t>실감 콘텐츠 프로듀서, 실시간 애니메이터</t>
